--- a/excelAvancado/aula06/Funcoes_Banco_Dados_Excel.xlsx
+++ b/excelAvancado/aula06/Funcoes_Banco_Dados_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\excelAvancado\aula06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0AF363B-C9A8-4AA8-B6C5-1C53CA739CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F0DE71-2FED-45F3-8FD1-39A756B45918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_Dados" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Exercicios" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -212,6 +211,9 @@
   <si>
     <t>8. Conte quantos produtos da categoria TI existem na tabela.</t>
   </si>
+  <si>
+    <t>&gt;5000</t>
+  </si>
 </sst>
 </file>
 
@@ -260,7 +262,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,6 +273,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -296,19 +304,25 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -319,20 +333,49 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -343,6 +386,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AF566B17-9834-49AC-972E-F64637647361}" name="Base_Dados" displayName="Base_Dados" ref="A1:H201" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="1">
+  <autoFilter ref="A1:H201" xr:uid="{AF566B17-9834-49AC-972E-F64637647361}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{10ECA7CE-95B9-442E-B950-5D6C82938898}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{C07F38E2-C1DF-471C-92C2-829061B3376E}" name="Produto"/>
+    <tableColumn id="3" xr3:uid="{7ABF7A3A-7AEC-46A3-BA2F-7F1B60802967}" name="Categoria"/>
+    <tableColumn id="4" xr3:uid="{A13371E5-F6B8-46CB-8E48-F0414CB03278}" name="Vendedor"/>
+    <tableColumn id="5" xr3:uid="{661E26E9-14AC-4AE8-A1FE-D8A6E1B85519}" name="Região"/>
+    <tableColumn id="6" xr3:uid="{621B6EBC-994B-4CC3-9B2D-663353EDEC1B}" name="Quantidade"/>
+    <tableColumn id="7" xr3:uid="{BC5A7C45-F5F3-4C66-BE88-811BC4A9E880}" name="Valor Unitário"/>
+    <tableColumn id="8" xr3:uid="{26A6242C-9F55-4534-BF35-05CF4838C66B}" name="Valor Total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,84 +693,86 @@
   <dimension ref="A1:H201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="8" width="20" customWidth="1"/>
+    <col min="1" max="6" width="14.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>8</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="4">
         <v>180</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>1440</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3">
         <v>7</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>180</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>1260</v>
       </c>
     </row>
@@ -741,28 +803,28 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>120</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>1800</v>
       </c>
     </row>
@@ -793,28 +855,28 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>250</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>2000</v>
       </c>
     </row>
@@ -845,28 +907,28 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>15</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9">
         <v>900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>13500</v>
       </c>
     </row>
@@ -897,28 +959,28 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11">
         <v>8</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11">
         <v>900</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>7200</v>
       </c>
     </row>
@@ -949,28 +1011,28 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>3</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>900</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <v>2700</v>
       </c>
     </row>
@@ -1001,28 +1063,28 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>120</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15">
         <v>240</v>
       </c>
     </row>
@@ -1053,28 +1115,28 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>4</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17">
         <v>1200</v>
       </c>
     </row>
@@ -1105,28 +1167,28 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>15</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19">
         <v>1200</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <v>18000</v>
       </c>
     </row>
@@ -1157,28 +1219,28 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21">
         <v>1800</v>
       </c>
     </row>
@@ -1209,28 +1271,28 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="3">
-        <v>9</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23">
+        <v>9</v>
+      </c>
+      <c r="G23">
         <v>180</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>1620</v>
       </c>
     </row>
@@ -1261,28 +1323,28 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>15</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25">
         <v>900</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <v>13500</v>
       </c>
     </row>
@@ -1313,28 +1375,28 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="3">
-        <v>9</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <v>40500</v>
       </c>
     </row>
@@ -1365,28 +1427,28 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29">
         <v>7</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29">
         <v>4500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <v>31500</v>
       </c>
     </row>
@@ -1417,28 +1479,28 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31">
         <v>4</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>4500</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31">
         <v>18000</v>
       </c>
     </row>
@@ -1469,28 +1531,28 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33">
         <v>4</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33">
         <v>900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33">
         <v>3600</v>
       </c>
     </row>
@@ -1521,28 +1583,28 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>26</v>
       </c>
-      <c r="F35" s="3">
-        <v>13</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="F35">
+        <v>13</v>
+      </c>
+      <c r="G35">
         <v>900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35">
         <v>11700</v>
       </c>
     </row>
@@ -1573,28 +1635,28 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
         <v>10</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37">
         <v>6</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37">
         <v>180</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37">
         <v>1080</v>
       </c>
     </row>
@@ -1625,28 +1687,28 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39">
         <v>15</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39">
         <v>120</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39">
         <v>1800</v>
       </c>
     </row>
@@ -1677,28 +1739,28 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41">
         <v>12</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41">
         <v>180</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41">
         <v>2160</v>
       </c>
     </row>
@@ -1729,28 +1791,28 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="3" t="s">
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
         <v>11</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43">
         <v>12</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43">
         <v>10800</v>
       </c>
     </row>
@@ -1781,28 +1843,28 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" t="s">
         <v>28</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45">
         <v>1</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45">
         <v>1200</v>
       </c>
     </row>
@@ -1833,28 +1895,28 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" t="s">
         <v>26</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47">
         <v>11</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47">
         <v>700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47">
         <v>7700</v>
       </c>
     </row>
@@ -1885,28 +1947,28 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49">
         <v>6</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49">
         <v>1200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49">
         <v>7200</v>
       </c>
     </row>
@@ -1937,28 +1999,28 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51">
         <v>250</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51">
         <v>250</v>
       </c>
     </row>
@@ -1989,28 +2051,28 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" t="s">
         <v>28</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" t="s">
         <v>11</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53">
         <v>4</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53">
         <v>4500</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53">
         <v>18000</v>
       </c>
     </row>
@@ -2041,28 +2103,28 @@
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="3">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="3">
+      <c r="E55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55">
         <v>1</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55">
         <v>700</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55">
         <v>700</v>
       </c>
     </row>
@@ -2093,28 +2155,28 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="3">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57">
         <v>15</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57">
         <v>18000</v>
       </c>
     </row>
@@ -2145,28 +2207,28 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="3">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59">
         <v>12</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59">
         <v>10800</v>
       </c>
     </row>
@@ -2197,28 +2259,28 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="3">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" t="s">
         <v>11</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61">
         <v>2</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61">
         <v>1400</v>
       </c>
     </row>
@@ -2249,28 +2311,28 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="3">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" t="s">
         <v>18</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" t="s">
         <v>16</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63">
         <v>3</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63">
         <v>900</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63">
         <v>2700</v>
       </c>
     </row>
@@ -2301,28 +2363,28 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" t="s">
         <v>17</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="3">
-        <v>14</v>
-      </c>
-      <c r="G65" s="3">
+      <c r="E65" t="s">
+        <v>14</v>
+      </c>
+      <c r="F65">
+        <v>14</v>
+      </c>
+      <c r="G65">
         <v>700</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65">
         <v>9800</v>
       </c>
     </row>
@@ -2353,28 +2415,28 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="3">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" t="s">
         <v>25</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="3">
-        <v>14</v>
-      </c>
-      <c r="G67" s="3">
+      <c r="F67">
+        <v>14</v>
+      </c>
+      <c r="G67">
         <v>350</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67">
         <v>4900</v>
       </c>
     </row>
@@ -2405,28 +2467,28 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="3">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>7</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69">
         <v>250</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69">
         <v>1750</v>
       </c>
     </row>
@@ -2457,28 +2519,28 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="3">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" t="s">
         <v>27</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" t="s">
         <v>28</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71">
         <v>7</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71">
         <v>4500</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71">
         <v>31500</v>
       </c>
     </row>
@@ -2509,28 +2571,28 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="3">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" t="s">
         <v>15</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="3" t="s">
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
         <v>20</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" t="s">
         <v>26</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73">
         <v>3</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73">
         <v>120</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73">
         <v>360</v>
       </c>
     </row>
@@ -2561,28 +2623,28 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75" s="3">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" t="s">
         <v>8</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="s">
         <v>16</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75">
         <v>8</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75">
         <v>180</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75">
         <v>1440</v>
       </c>
     </row>
@@ -2613,28 +2675,28 @@
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A77" s="3">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
         <v>26</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77">
         <v>3</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77">
         <v>180</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77">
         <v>540</v>
       </c>
     </row>
@@ -2665,28 +2727,28 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="3">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="3" t="s">
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
         <v>12</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" t="s">
         <v>24</v>
       </c>
-      <c r="F79" s="3">
-        <v>14</v>
-      </c>
-      <c r="G79" s="3">
+      <c r="F79">
+        <v>14</v>
+      </c>
+      <c r="G79">
         <v>120</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79">
         <v>1680</v>
       </c>
     </row>
@@ -2717,28 +2779,28 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="3">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" t="s">
         <v>20</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" t="s">
         <v>11</v>
       </c>
-      <c r="F81" s="3">
-        <v>14</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="F81">
+        <v>14</v>
+      </c>
+      <c r="G81">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="H81">
         <v>63000</v>
       </c>
     </row>
@@ -2769,28 +2831,28 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="3">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" t="s">
         <v>19</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="3" t="s">
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" t="s">
         <v>24</v>
       </c>
-      <c r="F83" s="3">
-        <v>14</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="F83">
+        <v>14</v>
+      </c>
+      <c r="G83">
         <v>250</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83">
         <v>3500</v>
       </c>
     </row>
@@ -2821,28 +2883,28 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="3">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" t="s">
         <v>11</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85">
         <v>8</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85">
         <v>180</v>
       </c>
-      <c r="H85" s="3">
+      <c r="H85">
         <v>1440</v>
       </c>
     </row>
@@ -2873,28 +2935,28 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="3">
+      <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" t="s">
         <v>25</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" t="s">
         <v>23</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" t="s">
         <v>12</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" t="s">
         <v>26</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87">
         <v>15</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87">
         <v>350</v>
       </c>
-      <c r="H87" s="3">
+      <c r="H87">
         <v>5250</v>
       </c>
     </row>
@@ -2925,28 +2987,28 @@
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="3">
+      <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" t="s">
         <v>22</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" t="s">
         <v>23</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89">
         <v>8</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89">
         <v>7200</v>
       </c>
     </row>
@@ -2977,28 +3039,28 @@
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="3">
+      <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" t="s">
         <v>23</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" t="s">
         <v>26</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91">
         <v>6</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91">
         <v>900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91">
         <v>5400</v>
       </c>
     </row>
@@ -3029,28 +3091,28 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="3">
+      <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" t="s">
         <v>28</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" s="3">
+      <c r="D93" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93">
         <v>8</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93">
         <v>4500</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H93">
         <v>36000</v>
       </c>
     </row>
@@ -3081,28 +3143,28 @@
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="3">
+      <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" t="s">
         <v>19</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="3" t="s">
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
         <v>16</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95">
         <v>11</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95">
         <v>250</v>
       </c>
-      <c r="H95" s="3">
+      <c r="H95">
         <v>2750</v>
       </c>
     </row>
@@ -3133,28 +3195,28 @@
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="3">
+      <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" t="s">
         <v>22</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" t="s">
         <v>23</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="D97" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97">
         <v>15</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97">
         <v>900</v>
       </c>
-      <c r="H97" s="3">
+      <c r="H97">
         <v>13500</v>
       </c>
     </row>
@@ -3185,28 +3247,28 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="3">
+      <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" t="s">
         <v>8</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="s">
         <v>26</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99">
         <v>12</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99">
         <v>180</v>
       </c>
-      <c r="H99" s="3">
+      <c r="H99">
         <v>2160</v>
       </c>
     </row>
@@ -3237,28 +3299,28 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" s="3">
+      <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" t="s">
         <v>28</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" t="s">
         <v>12</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="E101" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101">
         <v>1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101">
         <v>9600</v>
       </c>
     </row>
@@ -3289,28 +3351,28 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A103" s="3">
+      <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" t="s">
         <v>29</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" t="s">
         <v>28</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F103" s="3">
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103">
         <v>2</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103">
         <v>1200</v>
       </c>
-      <c r="H103" s="3">
+      <c r="H103">
         <v>2400</v>
       </c>
     </row>
@@ -3341,28 +3403,28 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" s="3">
+      <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" t="s">
         <v>25</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" t="s">
         <v>23</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" t="s">
         <v>20</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" t="s">
         <v>24</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105">
         <v>11</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105">
         <v>350</v>
       </c>
-      <c r="H105" s="3">
+      <c r="H105">
         <v>3850</v>
       </c>
     </row>
@@ -3393,28 +3455,28 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" s="3">
+      <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" t="s">
         <v>29</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" t="s">
         <v>28</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" t="s">
         <v>20</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" t="s">
         <v>26</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107">
         <v>5</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107">
         <v>1200</v>
       </c>
-      <c r="H107" s="3">
+      <c r="H107">
         <v>6000</v>
       </c>
     </row>
@@ -3445,28 +3507,28 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A109" s="3">
+      <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="3" t="s">
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" t="s">
         <v>26</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109">
         <v>8</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109">
         <v>180</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109">
         <v>1440</v>
       </c>
     </row>
@@ -3497,28 +3559,28 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A111" s="3">
+      <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" t="s">
         <v>21</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" t="s">
         <v>18</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" t="s">
         <v>12</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" t="s">
         <v>24</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111">
         <v>2</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111">
         <v>900</v>
       </c>
-      <c r="H111" s="3">
+      <c r="H111">
         <v>1800</v>
       </c>
     </row>
@@ -3549,28 +3611,28 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A113" s="3">
+      <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" t="s">
         <v>15</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="3" t="s">
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" t="s">
         <v>16</v>
       </c>
-      <c r="E113" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F113" s="3">
+      <c r="E113" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113">
         <v>15</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113">
         <v>120</v>
       </c>
-      <c r="H113" s="3">
+      <c r="H113">
         <v>1800</v>
       </c>
     </row>
@@ -3601,28 +3663,28 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" s="3">
+      <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" t="s">
         <v>30</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="3" t="s">
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" t="s">
         <v>24</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115">
         <v>12</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115">
         <v>300</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115">
         <v>3600</v>
       </c>
     </row>
@@ -3653,28 +3715,28 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A117" s="3">
+      <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" t="s">
         <v>30</v>
       </c>
-      <c r="C117" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117" s="3" t="s">
+      <c r="C117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" t="s">
         <v>12</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" t="s">
         <v>26</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117">
         <v>7</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117">
         <v>300</v>
       </c>
-      <c r="H117" s="3">
+      <c r="H117">
         <v>2100</v>
       </c>
     </row>
@@ -3705,28 +3767,28 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A119" s="3">
+      <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="3" t="s">
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
         <v>26</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119">
         <v>7</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119">
         <v>180</v>
       </c>
-      <c r="H119" s="3">
+      <c r="H119">
         <v>1260</v>
       </c>
     </row>
@@ -3757,28 +3819,28 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A121" s="3">
+      <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" t="s">
         <v>17</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" t="s">
         <v>18</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" t="s">
         <v>20</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" t="s">
         <v>11</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121">
         <v>15</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121">
         <v>700</v>
       </c>
-      <c r="H121" s="3">
+      <c r="H121">
         <v>10500</v>
       </c>
     </row>
@@ -3809,28 +3871,28 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A123" s="3">
+      <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" t="s">
         <v>29</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" t="s">
         <v>28</v>
       </c>
-      <c r="D123" s="3" t="s">
+      <c r="D123" t="s">
         <v>12</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F123" s="3">
+      <c r="E123" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123">
         <v>1</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123">
         <v>1200</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123">
         <v>1200</v>
       </c>
     </row>
@@ -3861,28 +3923,28 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A125" s="3">
+      <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" t="s">
         <v>28</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" t="s">
         <v>11</v>
       </c>
-      <c r="F125" s="3">
-        <v>14</v>
-      </c>
-      <c r="G125" s="3">
+      <c r="F125">
+        <v>14</v>
+      </c>
+      <c r="G125">
         <v>1200</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125">
         <v>16800</v>
       </c>
     </row>
@@ -3913,28 +3975,28 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A127" s="3">
+      <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" t="s">
         <v>27</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" t="s">
         <v>28</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" s="3" t="s">
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
         <v>11</v>
       </c>
-      <c r="F127" s="3">
+      <c r="F127">
         <v>2</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127">
         <v>4500</v>
       </c>
-      <c r="H127" s="3">
+      <c r="H127">
         <v>9000</v>
       </c>
     </row>
@@ -3965,28 +4027,28 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A129" s="3">
+      <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" t="s">
         <v>30</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D129" s="3" t="s">
+      <c r="C129" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" t="s">
         <v>16</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F129" s="3">
+      <c r="E129" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129">
         <v>3</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129">
         <v>300</v>
       </c>
-      <c r="H129" s="3">
+      <c r="H129">
         <v>900</v>
       </c>
     </row>
@@ -4017,28 +4079,28 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A131" s="3">
+      <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" t="s">
         <v>27</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" t="s">
         <v>28</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" t="s">
         <v>16</v>
       </c>
-      <c r="E131" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F131" s="3">
+      <c r="E131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F131">
         <v>4</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131">
         <v>4500</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H131">
         <v>18000</v>
       </c>
     </row>
@@ -4069,28 +4131,28 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A133" s="3">
+      <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" t="s">
         <v>22</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" t="s">
         <v>23</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" t="s">
         <v>12</v>
       </c>
-      <c r="E133" s="3" t="s">
+      <c r="E133" t="s">
         <v>26</v>
       </c>
-      <c r="F133" s="3">
+      <c r="F133">
         <v>12</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133">
         <v>900</v>
       </c>
-      <c r="H133" s="3">
+      <c r="H133">
         <v>10800</v>
       </c>
     </row>
@@ -4121,28 +4183,28 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A135" s="3">
+      <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" t="s">
         <v>27</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" t="s">
         <v>28</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="3" t="s">
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
         <v>26</v>
       </c>
-      <c r="F135" s="3">
+      <c r="F135">
         <v>15</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135">
         <v>4500</v>
       </c>
-      <c r="H135" s="3">
+      <c r="H135">
         <v>67500</v>
       </c>
     </row>
@@ -4173,28 +4235,28 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A137" s="3">
+      <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" t="s">
         <v>22</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" t="s">
         <v>23</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D137" t="s">
         <v>16</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F137" s="3">
+      <c r="E137" t="s">
+        <v>14</v>
+      </c>
+      <c r="F137">
         <v>6</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G137">
         <v>900</v>
       </c>
-      <c r="H137" s="3">
+      <c r="H137">
         <v>5400</v>
       </c>
     </row>
@@ -4225,28 +4287,28 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A139" s="3">
+      <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" t="s">
         <v>17</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" t="s">
         <v>18</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" t="s">
         <v>20</v>
       </c>
-      <c r="E139" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F139" s="3">
+      <c r="E139" t="s">
+        <v>14</v>
+      </c>
+      <c r="F139">
         <v>2</v>
       </c>
-      <c r="G139" s="3">
+      <c r="G139">
         <v>700</v>
       </c>
-      <c r="H139" s="3">
+      <c r="H139">
         <v>1400</v>
       </c>
     </row>
@@ -4277,28 +4339,28 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A141" s="3">
+      <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" t="s">
         <v>17</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" t="s">
         <v>18</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D141" t="s">
         <v>20</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E141" t="s">
         <v>11</v>
       </c>
-      <c r="F141" s="3">
+      <c r="F141">
         <v>1</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G141">
         <v>700</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H141">
         <v>700</v>
       </c>
     </row>
@@ -4329,28 +4391,28 @@
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A143" s="3">
+      <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" t="s">
         <v>23</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" t="s">
         <v>20</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F143" s="3">
-        <v>13</v>
-      </c>
-      <c r="G143" s="3">
+      <c r="E143" t="s">
+        <v>14</v>
+      </c>
+      <c r="F143">
+        <v>13</v>
+      </c>
+      <c r="G143">
         <v>350</v>
       </c>
-      <c r="H143" s="3">
+      <c r="H143">
         <v>4550</v>
       </c>
     </row>
@@ -4381,28 +4443,28 @@
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A145" s="3">
+      <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" t="s">
         <v>17</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" t="s">
         <v>18</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F145" s="3">
+      <c r="D145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="s">
+        <v>14</v>
+      </c>
+      <c r="F145">
         <v>8</v>
       </c>
-      <c r="G145" s="3">
+      <c r="G145">
         <v>700</v>
       </c>
-      <c r="H145" s="3">
+      <c r="H145">
         <v>5600</v>
       </c>
     </row>
@@ -4433,28 +4495,28 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A147" s="3">
+      <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" t="s">
         <v>30</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="3" t="s">
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
         <v>24</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F147">
         <v>12</v>
       </c>
-      <c r="G147" s="3">
+      <c r="G147">
         <v>300</v>
       </c>
-      <c r="H147" s="3">
+      <c r="H147">
         <v>3600</v>
       </c>
     </row>
@@ -4485,28 +4547,28 @@
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A149" s="3">
+      <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" t="s">
         <v>27</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" t="s">
         <v>28</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" t="s">
         <v>10</v>
       </c>
-      <c r="E149" s="3" t="s">
+      <c r="E149" t="s">
         <v>26</v>
       </c>
-      <c r="F149" s="3">
+      <c r="F149">
         <v>7</v>
       </c>
-      <c r="G149" s="3">
+      <c r="G149">
         <v>4500</v>
       </c>
-      <c r="H149" s="3">
+      <c r="H149">
         <v>31500</v>
       </c>
     </row>
@@ -4537,28 +4599,28 @@
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A151" s="3">
+      <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" t="s">
         <v>15</v>
       </c>
-      <c r="C151" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="3" t="s">
+      <c r="C151" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" t="s">
         <v>24</v>
       </c>
-      <c r="F151" s="3">
+      <c r="F151">
         <v>6</v>
       </c>
-      <c r="G151" s="3">
+      <c r="G151">
         <v>120</v>
       </c>
-      <c r="H151" s="3">
+      <c r="H151">
         <v>720</v>
       </c>
     </row>
@@ -4589,28 +4651,28 @@
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A153" s="3">
+      <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" t="s">
         <v>29</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" t="s">
         <v>28</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" t="s">
         <v>12</v>
       </c>
-      <c r="E153" s="3" t="s">
+      <c r="E153" t="s">
         <v>24</v>
       </c>
-      <c r="F153" s="3">
-        <v>9</v>
-      </c>
-      <c r="G153" s="3">
+      <c r="F153">
+        <v>9</v>
+      </c>
+      <c r="G153">
         <v>1200</v>
       </c>
-      <c r="H153" s="3">
+      <c r="H153">
         <v>10800</v>
       </c>
     </row>
@@ -4641,28 +4703,28 @@
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A155" s="3">
+      <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" t="s">
         <v>19</v>
       </c>
-      <c r="C155" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F155" s="3">
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155">
         <v>4</v>
       </c>
-      <c r="G155" s="3">
+      <c r="G155">
         <v>250</v>
       </c>
-      <c r="H155" s="3">
+      <c r="H155">
         <v>1000</v>
       </c>
     </row>
@@ -4693,28 +4755,28 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A157" s="3">
+      <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" t="s">
         <v>19</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" s="3" t="s">
+      <c r="C157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="s">
         <v>24</v>
       </c>
-      <c r="F157" s="3">
-        <v>14</v>
-      </c>
-      <c r="G157" s="3">
+      <c r="F157">
+        <v>14</v>
+      </c>
+      <c r="G157">
         <v>250</v>
       </c>
-      <c r="H157" s="3">
+      <c r="H157">
         <v>3500</v>
       </c>
     </row>
@@ -4745,28 +4807,28 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A159" s="3">
+      <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" t="s">
         <v>22</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" t="s">
         <v>23</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" t="s">
         <v>16</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="E159" t="s">
         <v>24</v>
       </c>
-      <c r="F159" s="3">
+      <c r="F159">
         <v>4</v>
       </c>
-      <c r="G159" s="3">
+      <c r="G159">
         <v>900</v>
       </c>
-      <c r="H159" s="3">
+      <c r="H159">
         <v>3600</v>
       </c>
     </row>
@@ -4797,28 +4859,28 @@
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A161" s="3">
+      <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" t="s">
         <v>15</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" s="3" t="s">
+      <c r="C161" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" t="s">
         <v>10</v>
       </c>
-      <c r="E161" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F161" s="3">
+      <c r="E161" t="s">
+        <v>14</v>
+      </c>
+      <c r="F161">
         <v>1</v>
       </c>
-      <c r="G161" s="3">
+      <c r="G161">
         <v>120</v>
       </c>
-      <c r="H161" s="3">
+      <c r="H161">
         <v>120</v>
       </c>
     </row>
@@ -4849,28 +4911,28 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A163" s="3">
+      <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" t="s">
         <v>29</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" t="s">
         <v>28</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F163" s="3">
+      <c r="D163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="s">
+        <v>14</v>
+      </c>
+      <c r="F163">
         <v>12</v>
       </c>
-      <c r="G163" s="3">
+      <c r="G163">
         <v>1200</v>
       </c>
-      <c r="H163" s="3">
+      <c r="H163">
         <v>14400</v>
       </c>
     </row>
@@ -4901,28 +4963,28 @@
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A165" s="3">
+      <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" t="s">
         <v>25</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" t="s">
         <v>23</v>
       </c>
-      <c r="D165" s="3" t="s">
+      <c r="D165" t="s">
         <v>20</v>
       </c>
-      <c r="E165" s="3" t="s">
+      <c r="E165" t="s">
         <v>24</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165">
         <v>2</v>
       </c>
-      <c r="G165" s="3">
+      <c r="G165">
         <v>350</v>
       </c>
-      <c r="H165" s="3">
+      <c r="H165">
         <v>700</v>
       </c>
     </row>
@@ -4953,28 +5015,28 @@
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A167" s="3">
+      <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" t="s">
         <v>29</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" t="s">
         <v>28</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D167" t="s">
         <v>10</v>
       </c>
-      <c r="E167" s="3" t="s">
+      <c r="E167" t="s">
         <v>24</v>
       </c>
-      <c r="F167" s="3">
+      <c r="F167">
         <v>6</v>
       </c>
-      <c r="G167" s="3">
+      <c r="G167">
         <v>1200</v>
       </c>
-      <c r="H167" s="3">
+      <c r="H167">
         <v>7200</v>
       </c>
     </row>
@@ -5005,28 +5067,28 @@
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A169" s="3">
+      <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" t="s">
         <v>22</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" t="s">
         <v>23</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="3" t="s">
+      <c r="D169" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" t="s">
         <v>11</v>
       </c>
-      <c r="F169" s="3">
+      <c r="F169">
         <v>5</v>
       </c>
-      <c r="G169" s="3">
+      <c r="G169">
         <v>900</v>
       </c>
-      <c r="H169" s="3">
+      <c r="H169">
         <v>4500</v>
       </c>
     </row>
@@ -5057,28 +5119,28 @@
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A171" s="3">
+      <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" t="s">
         <v>29</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" t="s">
         <v>28</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="3" t="s">
+      <c r="D171" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" t="s">
         <v>26</v>
       </c>
-      <c r="F171" s="3">
+      <c r="F171">
         <v>15</v>
       </c>
-      <c r="G171" s="3">
+      <c r="G171">
         <v>1200</v>
       </c>
-      <c r="H171" s="3">
+      <c r="H171">
         <v>18000</v>
       </c>
     </row>
@@ -5109,28 +5171,28 @@
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A173" s="3">
+      <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" t="s">
         <v>27</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" t="s">
         <v>28</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="D173" t="s">
         <v>16</v>
       </c>
-      <c r="E173" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F173" s="3">
+      <c r="E173" t="s">
+        <v>14</v>
+      </c>
+      <c r="F173">
         <v>11</v>
       </c>
-      <c r="G173" s="3">
+      <c r="G173">
         <v>4500</v>
       </c>
-      <c r="H173" s="3">
+      <c r="H173">
         <v>49500</v>
       </c>
     </row>
@@ -5161,28 +5223,28 @@
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A175" s="3">
+      <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" t="s">
         <v>19</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D175" s="3" t="s">
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" t="s">
         <v>10</v>
       </c>
-      <c r="E175" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F175" s="3">
-        <v>9</v>
-      </c>
-      <c r="G175" s="3">
+      <c r="E175" t="s">
+        <v>14</v>
+      </c>
+      <c r="F175">
+        <v>9</v>
+      </c>
+      <c r="G175">
         <v>250</v>
       </c>
-      <c r="H175" s="3">
+      <c r="H175">
         <v>2250</v>
       </c>
     </row>
@@ -5213,28 +5275,28 @@
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A177" s="3">
+      <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" t="s">
         <v>29</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="C177" t="s">
         <v>28</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D177" t="s">
         <v>12</v>
       </c>
-      <c r="E177" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F177" s="3">
-        <v>13</v>
-      </c>
-      <c r="G177" s="3">
+      <c r="E177" t="s">
+        <v>14</v>
+      </c>
+      <c r="F177">
+        <v>13</v>
+      </c>
+      <c r="G177">
         <v>1200</v>
       </c>
-      <c r="H177" s="3">
+      <c r="H177">
         <v>15600</v>
       </c>
     </row>
@@ -5265,28 +5327,28 @@
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A179" s="3">
+      <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" t="s">
         <v>19</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D179" s="3" t="s">
+      <c r="C179" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" t="s">
         <v>12</v>
       </c>
-      <c r="E179" s="3" t="s">
+      <c r="E179" t="s">
         <v>11</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F179">
         <v>2</v>
       </c>
-      <c r="G179" s="3">
+      <c r="G179">
         <v>250</v>
       </c>
-      <c r="H179" s="3">
+      <c r="H179">
         <v>500</v>
       </c>
     </row>
@@ -5317,28 +5379,28 @@
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A181" s="3">
+      <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" t="s">
         <v>15</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D181" s="3" t="s">
+      <c r="C181" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" t="s">
         <v>12</v>
       </c>
-      <c r="E181" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F181" s="3">
+      <c r="E181" t="s">
+        <v>14</v>
+      </c>
+      <c r="F181">
         <v>11</v>
       </c>
-      <c r="G181" s="3">
+      <c r="G181">
         <v>120</v>
       </c>
-      <c r="H181" s="3">
+      <c r="H181">
         <v>1320</v>
       </c>
     </row>
@@ -5369,28 +5431,28 @@
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A183" s="3">
+      <c r="A183">
         <v>182</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" t="s">
         <v>19</v>
       </c>
-      <c r="C183" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D183" s="3" t="s">
+      <c r="C183" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" t="s">
         <v>12</v>
       </c>
-      <c r="E183" s="3" t="s">
+      <c r="E183" t="s">
         <v>26</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183">
         <v>2</v>
       </c>
-      <c r="G183" s="3">
+      <c r="G183">
         <v>250</v>
       </c>
-      <c r="H183" s="3">
+      <c r="H183">
         <v>500</v>
       </c>
     </row>
@@ -5421,28 +5483,28 @@
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A185" s="3">
+      <c r="A185">
         <v>184</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" t="s">
         <v>8</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D185" s="3" t="s">
+      <c r="C185" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" t="s">
         <v>12</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F185" s="3">
-        <v>13</v>
-      </c>
-      <c r="G185" s="3">
+      <c r="E185" t="s">
+        <v>14</v>
+      </c>
+      <c r="F185">
+        <v>13</v>
+      </c>
+      <c r="G185">
         <v>180</v>
       </c>
-      <c r="H185" s="3">
+      <c r="H185">
         <v>2340</v>
       </c>
     </row>
@@ -5473,28 +5535,28 @@
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A187" s="3">
+      <c r="A187">
         <v>186</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" t="s">
         <v>21</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="C187" t="s">
         <v>18</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E187" s="3" t="s">
+      <c r="D187" t="s">
+        <v>13</v>
+      </c>
+      <c r="E187" t="s">
         <v>24</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187">
         <v>8</v>
       </c>
-      <c r="G187" s="3">
+      <c r="G187">
         <v>900</v>
       </c>
-      <c r="H187" s="3">
+      <c r="H187">
         <v>7200</v>
       </c>
     </row>
@@ -5525,28 +5587,28 @@
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A189" s="3">
+      <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" t="s">
         <v>8</v>
       </c>
-      <c r="C189" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D189" s="3" t="s">
+      <c r="C189" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" t="s">
         <v>20</v>
       </c>
-      <c r="E189" s="3" t="s">
+      <c r="E189" t="s">
         <v>26</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189">
         <v>15</v>
       </c>
-      <c r="G189" s="3">
+      <c r="G189">
         <v>180</v>
       </c>
-      <c r="H189" s="3">
+      <c r="H189">
         <v>2700</v>
       </c>
     </row>
@@ -5577,28 +5639,28 @@
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A191" s="3">
+      <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" t="s">
         <v>27</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" t="s">
         <v>28</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E191" s="3" t="s">
+      <c r="D191" t="s">
+        <v>13</v>
+      </c>
+      <c r="E191" t="s">
         <v>24</v>
       </c>
-      <c r="F191" s="3">
+      <c r="F191">
         <v>1</v>
       </c>
-      <c r="G191" s="3">
+      <c r="G191">
         <v>4500</v>
       </c>
-      <c r="H191" s="3">
+      <c r="H191">
         <v>4500</v>
       </c>
     </row>
@@ -5629,28 +5691,28 @@
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A193" s="3">
+      <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" t="s">
         <v>8</v>
       </c>
-      <c r="C193" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D193" s="3" t="s">
+      <c r="C193" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" t="s">
         <v>10</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="E193" t="s">
         <v>24</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193">
         <v>1</v>
       </c>
-      <c r="G193" s="3">
+      <c r="G193">
         <v>180</v>
       </c>
-      <c r="H193" s="3">
+      <c r="H193">
         <v>180</v>
       </c>
     </row>
@@ -5681,28 +5743,28 @@
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A195" s="3">
+      <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" t="s">
         <v>27</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="C195" t="s">
         <v>28</v>
       </c>
-      <c r="D195" s="3" t="s">
+      <c r="D195" t="s">
         <v>16</v>
       </c>
-      <c r="E195" s="3" t="s">
+      <c r="E195" t="s">
         <v>24</v>
       </c>
-      <c r="F195" s="3">
+      <c r="F195">
         <v>7</v>
       </c>
-      <c r="G195" s="3">
+      <c r="G195">
         <v>4500</v>
       </c>
-      <c r="H195" s="3">
+      <c r="H195">
         <v>31500</v>
       </c>
     </row>
@@ -5733,28 +5795,28 @@
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A197" s="3">
+      <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" t="s">
         <v>15</v>
       </c>
-      <c r="C197" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E197" s="3" t="s">
+      <c r="C197" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" t="s">
+        <v>13</v>
+      </c>
+      <c r="E197" t="s">
         <v>26</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F197">
         <v>10</v>
       </c>
-      <c r="G197" s="3">
+      <c r="G197">
         <v>120</v>
       </c>
-      <c r="H197" s="3">
+      <c r="H197">
         <v>1200</v>
       </c>
     </row>
@@ -5785,28 +5847,28 @@
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A199" s="3">
+      <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" t="s">
         <v>21</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="C199" t="s">
         <v>18</v>
       </c>
-      <c r="D199" s="3" t="s">
+      <c r="D199" t="s">
         <v>10</v>
       </c>
-      <c r="E199" s="3" t="s">
+      <c r="E199" t="s">
         <v>11</v>
       </c>
-      <c r="F199" s="3">
-        <v>13</v>
-      </c>
-      <c r="G199" s="3">
+      <c r="F199">
+        <v>13</v>
+      </c>
+      <c r="G199">
         <v>900</v>
       </c>
-      <c r="H199" s="3">
+      <c r="H199">
         <v>11700</v>
       </c>
     </row>
@@ -5837,33 +5899,36 @@
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A201" s="5">
+      <c r="A201" s="8">
         <v>200</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="B201" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C201" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D201" s="5" t="s">
+      <c r="C201" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D201" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E201" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F201" s="5">
+      <c r="E201" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F201" s="8">
         <v>11</v>
       </c>
-      <c r="G201" s="5">
+      <c r="G201" s="8">
         <v>180</v>
       </c>
-      <c r="H201" s="5">
+      <c r="H201" s="8">
         <v>1980</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5873,21 +5938,21 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" customWidth="1"/>
     <col min="3" max="3" width="17.54296875" customWidth="1"/>
     <col min="6" max="6" width="13.90625" customWidth="1"/>
     <col min="7" max="7" width="26.26953125" customWidth="1"/>
-    <col min="8" max="8" width="40.6328125" customWidth="1"/>
+    <col min="8" max="8" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F1" t="s">
@@ -5896,19 +5961,19 @@
       <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4">
-        <f>DSUM(Base_Dados!A1:H201,"Valor Total",A1:A2)</f>
+      <c r="H1" s="3">
+        <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>223360</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="B2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" t="s">
@@ -5930,7 +5995,7 @@
         <v>40</v>
       </c>
       <c r="H3">
-        <f>DCOUNTA(Base_Dados!A1:H201,"Produto",Critérios!A1:A2)</f>
+        <f>DCOUNTA(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>35</v>
       </c>
     </row>
@@ -5941,7 +6006,7 @@
       <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <f>DAVERAGE(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>6381.7142857142853</v>
       </c>
@@ -5953,7 +6018,7 @@
       <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <f>DMAX(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>40500</v>
       </c>
@@ -5965,7 +6030,7 @@
       <c r="G6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <f>DMIN(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>120</v>
       </c>
@@ -5977,9 +6042,9 @@
       <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!A1:B2)</f>
-        <v>30260</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -5989,12 +6054,20 @@
       <c r="G8" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!C1:C2)</f>
         <v>1471350</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{F5A12B10-3874-4E05-A57B-FB7E6FD30E61}">
+      <formula1>"Ana, João, Lucas, Carlos, Marina"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{B5835F05-3A8A-4A26-8895-C8A25A165AA8}">
+      <formula1>"Periférico, Escritório, Hardware, TI"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6025,7 +6098,7 @@
       <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>223360</v>
       </c>
@@ -6061,7 +6134,7 @@
       <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <f>DAVERAGE(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>6381.7142857142853</v>
       </c>
@@ -6073,7 +6146,7 @@
       <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <f>DMAX(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>40500</v>
       </c>
@@ -6085,7 +6158,7 @@
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <f>DMIN(Base_Dados!A1:H201,"Valor Total",Critérios!A1:A2)</f>
         <v>120</v>
       </c>
@@ -6097,9 +6170,9 @@
       <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!A1:B2)</f>
-        <v>30260</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6109,7 +6182,7 @@
       <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <f>DSUM(Base_Dados!A1:H201,"Valor Total",Critérios!C1:C2)</f>
         <v>1471350</v>
       </c>
@@ -6121,58 +6194,172 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="64.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B3" s="3">
+        <f>DSUM(Base_Dados[#All],"Valor Total",A14:A15)</f>
+        <v>164630</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <f>DCOUNT(Base_Dados[#All],"Valor Total",A17:A18)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3">
+        <f>DAVERAGE(Base_Dados[#All],"Valor Total",B14:B15)</f>
+        <v>5285.9375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B6" s="3">
+        <f>DMAX(Base_Dados[#All],"Valor Total",A20:A21)</f>
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <f>DMIN(Base_Dados[#All],"valor total",B20:B21)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B8" s="3">
+        <f>DSUM(Base_Dados[#All],"Valor Total", A23:B24)</f>
+        <v>84500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B9" s="3">
+        <f>DSUM(Base_Dados[#All],"valor total",C14:C15)</f>
+        <v>1223350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>57</v>
       </c>
+      <c r="B10">
+        <f>DCOUNT(Base_Dados[#All],"ID",B17:B18)</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18 B21" xr:uid="{74ED06ED-F170-40D5-88D4-41AC13AFF6E2}">
+      <formula1>"Periférico, Escritório, Hardware, TI"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A15 A18 A21 A24" xr:uid="{1C93B700-C333-4856-99E2-15FCBA110B04}">
+      <formula1>"Ana, João, Lucas, Carlos, Marina"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24" xr:uid="{11814F86-1BB5-4490-8754-E91A0FF343E6}">
+      <formula1>"Oeste, Norte, Sul, Leste"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>